--- a/Result/profitability/5206.xlsx
+++ b/Result/profitability/5206.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.94625</v>
+        <v>0.8225</v>
       </c>
       <c r="N2" t="n">
-        <v>30.11</v>
+        <v>30.5075</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.7187499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>28.48</v>
+        <v>31.60125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5749999999999998</v>
+        <v>0.5624999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>29.72125</v>
+        <v>30.64125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3262499999999999</v>
+        <v>0.01749999999999993</v>
       </c>
       <c r="N5" t="n">
-        <v>30.52625</v>
+        <v>31.72625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1225000000000001</v>
+        <v>0.01374999999999993</v>
       </c>
       <c r="N6" t="n">
-        <v>30.86875</v>
+        <v>31.8175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1187500000000001</v>
+        <v>0.02124999999999993</v>
       </c>
       <c r="N7" t="n">
-        <v>29.76</v>
+        <v>31.30375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09875000000000009</v>
+        <v>-0.2962500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>32.22125</v>
+        <v>32.3025</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.68</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4900000000000002</v>
+        <v>-0.4900000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>31.43375</v>
@@ -1899,7 +1899,7 @@
         <v>-0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3562500000000002</v>
+        <v>-0.3562500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>39.26875</v>
@@ -2029,7 +2029,7 @@
         <v>-0.2900000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>38.70874999999999</v>
+        <v>38.70875</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5206</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>600</v>
+      </c>
+      <c r="D75" t="n">
+        <v>356</v>
+      </c>
+      <c r="E75" t="n">
+        <v>244</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>185</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>195</v>
+      </c>
+      <c r="K75" t="n">
+        <v>156</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.09875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.4375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6448979591836734</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01624999999999988</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7395209580838323</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.599999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3091787439613525</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
